--- a/salidas/empresas/BAC.xlsx
+++ b/salidas/empresas/BAC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.34963607788086</v>
+        <v>28.34963989257812</v>
       </c>
       <c r="C2" t="n">
         <v>44.22999954223633</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>29.38801002502441</v>
+        <v>29.38799858093262</v>
       </c>
       <c r="C3" t="n">
         <v>45.84999847412109</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>29.5111255645752</v>
+        <v>29.51113128662109</v>
       </c>
       <c r="C4" t="n">
         <v>45.54000091552734</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.3494758605957</v>
+        <v>32.3494873046875</v>
       </c>
       <c r="C5" t="n">
         <v>49.91999816894531</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.68983459472656</v>
+        <v>31.68984985351562</v>
       </c>
       <c r="C6" t="n">
         <v>48.40000152587891</v>
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>33.73920822143555</v>
+        <v>33.73920440673828</v>
       </c>
       <c r="C8" t="n">
         <v>51.52999877929688</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>34.06475067138672</v>
+        <v>34.06473922729492</v>
       </c>
       <c r="C9" t="n">
         <v>51.47000122070312</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>35.45459365844727</v>
+        <v>35.4545783996582</v>
       </c>
       <c r="C10" t="n">
         <v>53.56999969482422</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>35.65314865112305</v>
+        <v>35.65315246582031</v>
       </c>
       <c r="C11" t="n">
         <v>53.86999893188477</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>35.70389175415039</v>
+        <v>35.70388412475586</v>
       </c>
       <c r="C13" t="n">
         <v>53.38999938964844</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>35.16221237182617</v>
+        <v>35.16220855712891</v>
       </c>
       <c r="C14" t="n">
         <v>52.58000183105469</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>34.37081909179688</v>
+        <v>34.37081146240234</v>
       </c>
       <c r="C15" t="n">
         <v>50.83000183105469</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>34.499267578125</v>
+        <v>34.4992790222168</v>
       </c>
       <c r="C16" t="n">
         <v>51.02000045776367</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>34.41814041137695</v>
+        <v>34.41813659667969</v>
       </c>
       <c r="C17" t="n">
         <v>50.90000152587891</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>34.66894149780273</v>
+        <v>34.66893005371094</v>
       </c>
       <c r="C18" t="n">
         <v>50.70999908447266</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>33.42463684082031</v>
+        <v>33.42464828491211</v>
       </c>
       <c r="C19" t="n">
         <v>48.88999938964844</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.41964340209961</v>
+        <v>32.41965103149414</v>
       </c>
       <c r="C20" t="n">
         <v>47.41999816894531</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>34.64841461181641</v>
+        <v>34.64841842651367</v>
       </c>
       <c r="C21" t="n">
         <v>50.68000030517578</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.42643356323242</v>
+        <v>33.42640686035156</v>
       </c>
       <c r="C23" t="n">
         <v>48.27999877929688</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>31.93787956237793</v>
+        <v>31.9378833770752</v>
       </c>
       <c r="C24" t="n">
         <v>46.13000106811523</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>28.98099708557129</v>
+        <v>28.98101234436035</v>
       </c>
       <c r="C25" t="n">
         <v>41.2599983215332</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.01093864440918</v>
+        <v>31.01094818115234</v>
       </c>
       <c r="C26" t="n">
         <v>44.15000152587891</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.91335487365723</v>
+        <v>27.91336822509766</v>
       </c>
       <c r="C27" t="n">
         <v>39.7400016784668</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>27.07478904724121</v>
+        <v>27.07479095458984</v>
       </c>
       <c r="C28" t="n">
         <v>37.90999984741211</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>26.81054496765137</v>
+        <v>26.81054306030273</v>
       </c>
       <c r="C29" t="n">
         <v>37.54000091552734</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>24.28947257995605</v>
+        <v>24.28946304321289</v>
       </c>
       <c r="C30" t="n">
         <v>34.0099983215332</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>17.38158798217773</v>
+        <v>17.3815803527832</v>
       </c>
       <c r="C31" t="n">
         <v>23.8700008392334</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>23.9570140838623</v>
+        <v>23.95701789855957</v>
       </c>
       <c r="C32" t="n">
         <v>32.90000152587891</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>22.67542266845703</v>
+        <v>22.67541694641113</v>
       </c>
       <c r="C33" t="n">
         <v>31.13999938964844</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>17.9521484375</v>
+        <v>17.95214462280273</v>
       </c>
       <c r="C35" t="n">
         <v>24.17000007629395</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>12.06960582733154</v>
+        <v>12.06960391998291</v>
       </c>
       <c r="C36" t="n">
         <v>16.25</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.69603633880615</v>
+        <v>10.69603538513184</v>
       </c>
       <c r="C37" t="n">
         <v>14.07999992370605</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>4.998573303222656</v>
+        <v>4.998574733734131</v>
       </c>
       <c r="C38" t="n">
         <v>6.579999923706055</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>3.00066351890564</v>
+        <v>3.000663280487061</v>
       </c>
       <c r="C39" t="n">
         <v>3.950000047683716</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>5.195124626159668</v>
+        <v>5.195125102996826</v>
       </c>
       <c r="C40" t="n">
         <v>6.820000171661377</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>6.802415370941162</v>
+        <v>6.802414417266846</v>
       </c>
       <c r="C41" t="n">
         <v>8.930000305175781</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>8.58491039276123</v>
+        <v>8.584905624389648</v>
       </c>
       <c r="C42" t="n">
         <v>11.27000045776367</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.06389904022217</v>
+        <v>10.06390190124512</v>
       </c>
       <c r="C43" t="n">
         <v>13.19999980926514</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.27614402770996</v>
+        <v>11.27614212036133</v>
       </c>
       <c r="C44" t="n">
         <v>14.78999996185303</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.41091060638428</v>
+        <v>13.41090965270996</v>
       </c>
       <c r="C45" t="n">
         <v>17.59000015258789</v>
@@ -1324,11 +1336,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.90793037414551</v>
+        <v>12.90792942047119</v>
       </c>
       <c r="C46" t="n">
         <v>16.92000007629395</v>
@@ -1349,11 +1361,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>11.12279605865479</v>
+        <v>11.1227970123291</v>
       </c>
       <c r="C47" t="n">
         <v>14.57999992370605</v>
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,11 +1411,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>11.49620628356934</v>
+        <v>11.49620819091797</v>
       </c>
       <c r="C49" t="n">
         <v>15.0600004196167</v>
@@ -1424,11 +1436,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>11.58780860900879</v>
+        <v>11.58780670166016</v>
       </c>
       <c r="C50" t="n">
         <v>15.18000030517578</v>
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,11 +1486,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>13.6342658996582</v>
+        <v>13.63426399230957</v>
       </c>
       <c r="C52" t="n">
         <v>17.85000038146973</v>
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,11 +1536,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.02260112762451</v>
+        <v>12.02259349822998</v>
       </c>
       <c r="C54" t="n">
         <v>15.73999977111816</v>
@@ -1549,11 +1561,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>10.9832706451416</v>
+        <v>10.98327159881592</v>
       </c>
       <c r="C55" t="n">
         <v>14.36999988555908</v>
@@ -1574,11 +1586,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>10.73104763031006</v>
+        <v>10.73104476928711</v>
       </c>
       <c r="C56" t="n">
         <v>14.03999996185303</v>
@@ -1599,11 +1611,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>9.523419380187988</v>
+        <v>9.523422241210938</v>
       </c>
       <c r="C57" t="n">
         <v>12.46000003814697</v>
@@ -1624,11 +1636,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>10.02062892913818</v>
+        <v>10.02062797546387</v>
       </c>
       <c r="C58" t="n">
         <v>13.10000038146973</v>
@@ -1649,11 +1661,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>8.758482933044434</v>
+        <v>8.75848388671875</v>
       </c>
       <c r="C59" t="n">
         <v>11.44999980926514</v>
@@ -1674,11 +1686,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>8.376019477844238</v>
+        <v>8.376023292541504</v>
       </c>
       <c r="C60" t="n">
         <v>10.94999980926514</v>
@@ -1699,11 +1711,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>10.21353816986084</v>
+        <v>10.21353721618652</v>
       </c>
       <c r="C61" t="n">
         <v>13.34000015258789</v>
@@ -1724,11 +1736,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>10.51213264465332</v>
+        <v>10.51213455200195</v>
       </c>
       <c r="C62" t="n">
         <v>13.72999954223633</v>
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1776,11 +1788,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>10.21321487426758</v>
+        <v>10.21321392059326</v>
       </c>
       <c r="C64" t="n">
         <v>13.32999992370605</v>
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>9.408723831176758</v>
+        <v>9.408720016479492</v>
       </c>
       <c r="C65" t="n">
         <v>12.27999973297119</v>
@@ -1830,11 +1842,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>9.002647399902344</v>
+        <v>9.002642631530762</v>
       </c>
       <c r="C66" t="n">
         <v>11.75</v>
@@ -1857,11 +1869,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>8.404513359069824</v>
+        <v>8.404514312744141</v>
       </c>
       <c r="C67" t="n">
         <v>10.96000003814697</v>
@@ -1884,11 +1896,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.445973873138428</v>
+        <v>7.445969581604004</v>
       </c>
       <c r="C68" t="n">
         <v>9.710000038146973</v>
@@ -1911,11 +1923,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>6.272768497467041</v>
+        <v>6.272770404815674</v>
       </c>
       <c r="C69" t="n">
         <v>8.170000076293945</v>
@@ -1938,11 +1950,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.698818683624268</v>
+        <v>4.698817729949951</v>
       </c>
       <c r="C70" t="n">
         <v>6.119999885559082</v>
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -1992,11 +2004,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>4.184965133666992</v>
+        <v>4.184967041015625</v>
       </c>
       <c r="C72" t="n">
         <v>5.440000057220459</v>
@@ -2019,11 +2031,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>4.277281761169434</v>
+        <v>4.277278900146484</v>
       </c>
       <c r="C73" t="n">
         <v>5.559999942779541</v>
@@ -2046,11 +2058,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>5.485073089599609</v>
+        <v>5.485074043273926</v>
       </c>
       <c r="C74" t="n">
         <v>7.130000114440918</v>
@@ -2073,7 +2085,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2102,7 +2114,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2131,11 +2143,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>6.246675491333008</v>
+        <v>6.246677398681641</v>
       </c>
       <c r="C77" t="n">
         <v>8.109999656677246</v>
@@ -2160,11 +2172,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>5.668910026550293</v>
+        <v>5.668910980224609</v>
       </c>
       <c r="C78" t="n">
         <v>7.349999904632568</v>
@@ -2187,11 +2199,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>6.309073925018311</v>
+        <v>6.309073448181152</v>
       </c>
       <c r="C79" t="n">
         <v>8.180000305175781</v>
@@ -2214,11 +2226,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>5.661199569702148</v>
+        <v>5.661196708679199</v>
       </c>
       <c r="C80" t="n">
         <v>7.340000152587891</v>
@@ -2241,11 +2253,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>6.162529468536377</v>
+        <v>6.162529945373535</v>
       </c>
       <c r="C81" t="n">
         <v>7.989999771118164</v>
@@ -2270,11 +2282,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>6.818929672241211</v>
+        <v>6.818928718566895</v>
       </c>
       <c r="C82" t="n">
         <v>8.829999923706055</v>
@@ -2299,11 +2311,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>7.197331428527832</v>
+        <v>7.197329044342041</v>
       </c>
       <c r="C83" t="n">
         <v>9.319999694824219</v>
@@ -2328,11 +2340,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>7.614343166351318</v>
+        <v>7.61434268951416</v>
       </c>
       <c r="C84" t="n">
         <v>9.859999656677246</v>
@@ -2357,11 +2369,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>8.974830627441406</v>
+        <v>8.974827766418457</v>
       </c>
       <c r="C85" t="n">
         <v>11.60999965667725</v>
@@ -2386,11 +2398,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>8.750651359558105</v>
+        <v>8.750653266906738</v>
       </c>
       <c r="C86" t="n">
         <v>11.31999969482422</v>
@@ -2415,11 +2427,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>8.688885688781738</v>
+        <v>8.688886642456055</v>
       </c>
       <c r="C87" t="n">
         <v>11.22999954223633</v>
@@ -2444,11 +2456,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.423921585083008</v>
+        <v>9.423922538757324</v>
       </c>
       <c r="C88" t="n">
         <v>12.18000030517578</v>
@@ -2473,11 +2485,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>9.524503707885742</v>
+        <v>9.524506568908691</v>
       </c>
       <c r="C89" t="n">
         <v>12.3100004196167</v>
@@ -2502,11 +2514,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>10.56903076171875</v>
+        <v>10.56902694702148</v>
       </c>
       <c r="C90" t="n">
         <v>13.65999984741211</v>
@@ -2531,11 +2543,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>9.957504272460938</v>
+        <v>9.95750617980957</v>
       </c>
       <c r="C91" t="n">
         <v>12.85999965667725</v>
@@ -2560,11 +2572,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>11.30479049682617</v>
+        <v>11.30478763580322</v>
       </c>
       <c r="C92" t="n">
         <v>14.60000038146973</v>
@@ -2589,11 +2601,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>10.93312358856201</v>
+        <v>10.9331226348877</v>
       </c>
       <c r="C93" t="n">
         <v>14.11999988555908</v>
@@ -2618,7 +2630,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2647,11 +2659,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>10.82457065582275</v>
+        <v>10.82457637786865</v>
       </c>
       <c r="C95" t="n">
         <v>13.97000026702881</v>
@@ -2676,11 +2688,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>12.25803852081299</v>
+        <v>12.25803565979004</v>
       </c>
       <c r="C96" t="n">
         <v>15.81999969482422</v>
@@ -2705,11 +2717,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>12.07209205627441</v>
+        <v>12.07209300994873</v>
       </c>
       <c r="C97" t="n">
         <v>15.56999969482422</v>
@@ -2734,11 +2746,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>12.98699951171875</v>
+        <v>12.98699760437012</v>
       </c>
       <c r="C98" t="n">
         <v>16.75</v>
@@ -2763,11 +2775,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>12.81642150878906</v>
+        <v>12.81642532348633</v>
       </c>
       <c r="C99" t="n">
         <v>16.53000068664551</v>
@@ -2792,11 +2804,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>13.34388160705566</v>
+        <v>13.34387493133545</v>
       </c>
       <c r="C100" t="n">
         <v>17.20000076293945</v>
@@ -2821,11 +2833,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>11.74571323394775</v>
+        <v>11.74571514129639</v>
       </c>
       <c r="C101" t="n">
         <v>15.14000034332275</v>
@@ -2850,11 +2862,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>11.74571323394775</v>
+        <v>11.74571514129639</v>
       </c>
       <c r="C102" t="n">
         <v>15.14000034332275</v>
@@ -2879,7 +2891,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2908,11 +2920,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>11.83867168426514</v>
+        <v>11.83866500854492</v>
       </c>
       <c r="C104" t="n">
         <v>15.25</v>
@@ -2937,11 +2949,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>12.49076557159424</v>
+        <v>12.49076461791992</v>
       </c>
       <c r="C105" t="n">
         <v>16.09000015258789</v>
@@ -2966,11 +2978,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>13.27682209014893</v>
+        <v>13.27681827545166</v>
       </c>
       <c r="C106" t="n">
         <v>17.04999923706055</v>
@@ -2995,11 +3007,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>13.36247730255127</v>
+        <v>13.362473487854</v>
       </c>
       <c r="C107" t="n">
         <v>17.15999984741211</v>
@@ -3024,11 +3036,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>13.26903533935547</v>
+        <v>13.26903820037842</v>
       </c>
       <c r="C108" t="n">
         <v>17.04000091552734</v>
@@ -3053,11 +3065,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>13.97166061401367</v>
+        <v>13.97165870666504</v>
       </c>
       <c r="C109" t="n">
         <v>17.88999938964844</v>
@@ -3082,11 +3094,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>11.83178901672363</v>
+        <v>11.83178520202637</v>
       </c>
       <c r="C110" t="n">
         <v>15.14999961853027</v>
@@ -3111,7 +3123,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3140,11 +3152,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>12.05680656433105</v>
+        <v>12.05680370330811</v>
       </c>
       <c r="C112" t="n">
         <v>15.39000034332275</v>
@@ -3169,11 +3181,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>12.47985172271729</v>
+        <v>12.47984886169434</v>
       </c>
       <c r="C113" t="n">
         <v>15.93000030517578</v>
@@ -3198,11 +3210,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>12.92639923095703</v>
+        <v>12.92640209197998</v>
       </c>
       <c r="C114" t="n">
         <v>16.5</v>
@@ -3227,11 +3239,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>13.37376594543457</v>
+        <v>13.3737678527832</v>
       </c>
       <c r="C115" t="n">
         <v>17.02000045776367</v>
@@ -3256,11 +3268,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>14.04953289031982</v>
+        <v>14.04952621459961</v>
       </c>
       <c r="C116" t="n">
         <v>17.8799991607666</v>
@@ -3285,11 +3297,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>12.83944892883301</v>
+        <v>12.83944988250732</v>
       </c>
       <c r="C117" t="n">
         <v>16.34000015258789</v>
@@ -3314,11 +3326,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.28167915344238</v>
+        <v>12.2816801071167</v>
       </c>
       <c r="C118" t="n">
         <v>15.57999992370605</v>
@@ -3343,11 +3355,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>13.22763633728027</v>
+        <v>13.22763729095459</v>
       </c>
       <c r="C119" t="n">
         <v>16.78000068664551</v>
@@ -3372,11 +3384,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>13.74003124237061</v>
+        <v>13.74002838134766</v>
       </c>
       <c r="C120" t="n">
         <v>17.43000030517578</v>
@@ -3401,11 +3413,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.30439853668213</v>
+        <v>13.30440139770508</v>
       </c>
       <c r="C121" t="n">
         <v>16.82999992370605</v>
@@ -3430,11 +3442,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>11.17791080474854</v>
+        <v>11.17791271209717</v>
       </c>
       <c r="C122" t="n">
         <v>14.14000034332275</v>
@@ -3459,11 +3471,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>9.897274971008301</v>
+        <v>9.897273063659668</v>
       </c>
       <c r="C123" t="n">
         <v>12.52000045776367</v>
@@ -3488,11 +3500,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>10.72845840454102</v>
+        <v>10.7284631729126</v>
       </c>
       <c r="C124" t="n">
         <v>13.52000045776367</v>
@@ -3517,11 +3529,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>11.55372905731201</v>
+        <v>11.55372714996338</v>
       </c>
       <c r="C125" t="n">
         <v>14.5600004196167</v>
@@ -3546,11 +3558,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>11.73623847961426</v>
+        <v>11.73623371124268</v>
       </c>
       <c r="C126" t="n">
         <v>14.78999996185303</v>
@@ -3575,7 +3587,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3604,7 +3616,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3633,11 +3645,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>12.91074752807617</v>
+        <v>12.91074848175049</v>
       </c>
       <c r="C129" t="n">
         <v>16.13999938964844</v>
@@ -3662,11 +3674,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>12.51878547668457</v>
+        <v>12.51878452301025</v>
       </c>
       <c r="C130" t="n">
         <v>15.64999961853027</v>
@@ -3691,11 +3703,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>13.1987190246582</v>
+        <v>13.19872379302979</v>
       </c>
       <c r="C131" t="n">
         <v>16.5</v>
@@ -3720,11 +3732,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>16.95703887939453</v>
+        <v>16.9570426940918</v>
       </c>
       <c r="C132" t="n">
         <v>21.1200008392334</v>
@@ -3749,11 +3761,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>17.74387741088867</v>
+        <v>17.74387359619141</v>
       </c>
       <c r="C133" t="n">
         <v>22.10000038146973</v>
@@ -3778,7 +3790,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3807,11 +3819,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>19.81533050537109</v>
+        <v>19.8153247833252</v>
       </c>
       <c r="C135" t="n">
         <v>24.68000030517578</v>
@@ -3836,11 +3848,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>18.9979076385498</v>
+        <v>18.99790954589844</v>
       </c>
       <c r="C136" t="n">
         <v>23.59000015258789</v>
@@ -3865,11 +3877,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>18.79657936096191</v>
+        <v>18.79657745361328</v>
       </c>
       <c r="C137" t="n">
         <v>23.34000015258789</v>
@@ -3894,11 +3906,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>18.10689353942871</v>
+        <v>18.10688972473145</v>
       </c>
       <c r="C138" t="n">
         <v>22.40999984741211</v>
@@ -3923,7 +3935,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3952,11 +3964,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>19.48854446411133</v>
+        <v>19.4885425567627</v>
       </c>
       <c r="C140" t="n">
         <v>24.1200008392334</v>
@@ -3981,11 +3993,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>19.40144157409668</v>
+        <v>19.40143966674805</v>
       </c>
       <c r="C141" t="n">
         <v>23.88999938964844</v>
@@ -4010,11 +4022,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>20.57901000976562</v>
+        <v>20.57900810241699</v>
       </c>
       <c r="C142" t="n">
         <v>25.34000015258789</v>
@@ -4039,11 +4051,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>22.24384689331055</v>
+        <v>22.24385070800781</v>
       </c>
       <c r="C143" t="n">
         <v>27.38999938964844</v>
@@ -4068,11 +4080,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>22.97477912902832</v>
+        <v>22.97478103637695</v>
       </c>
       <c r="C144" t="n">
         <v>28.17000007629395</v>
@@ -4097,11 +4109,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>24.0758113861084</v>
+        <v>24.07581329345703</v>
       </c>
       <c r="C145" t="n">
         <v>29.52000045776367</v>
@@ -4126,11 +4138,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>26.09843826293945</v>
+        <v>26.09843635559082</v>
       </c>
       <c r="C146" t="n">
         <v>32</v>
@@ -4155,11 +4167,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>26.17999267578125</v>
+        <v>26.17999649047852</v>
       </c>
       <c r="C147" t="n">
         <v>32.09999847412109</v>
@@ -4184,11 +4196,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>24.5509090423584</v>
+        <v>24.55090713500977</v>
       </c>
       <c r="C148" t="n">
         <v>29.98999977111816</v>
@@ -4213,7 +4225,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4242,11 +4254,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>23.87033653259277</v>
+        <v>23.87033462524414</v>
       </c>
       <c r="C150" t="n">
         <v>29.04000091552734</v>
@@ -4271,7 +4283,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4300,11 +4312,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>25.38278770446777</v>
+        <v>25.38278579711914</v>
       </c>
       <c r="C152" t="n">
         <v>30.8799991607666</v>
@@ -4329,7 +4341,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4358,11 +4370,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>24.33262634277344</v>
+        <v>24.33263397216797</v>
       </c>
       <c r="C154" t="n">
         <v>29.45999908447266</v>
@@ -4387,11 +4399,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>22.71375846862793</v>
+        <v>22.71376037597656</v>
       </c>
       <c r="C155" t="n">
         <v>27.5</v>
@@ -4416,7 +4428,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4445,11 +4457,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>20.46526527404785</v>
+        <v>20.46525764465332</v>
       </c>
       <c r="C157" t="n">
         <v>24.63999938964844</v>
@@ -4474,11 +4486,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>23.64635276794434</v>
+        <v>23.64634704589844</v>
       </c>
       <c r="C158" t="n">
         <v>28.46999931335449</v>
@@ -4503,11 +4515,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>24.27631759643555</v>
+        <v>24.27630996704102</v>
       </c>
       <c r="C159" t="n">
         <v>29.07999992370605</v>
@@ -4532,7 +4544,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4561,7 +4573,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4590,11 +4602,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>22.20598411560059</v>
+        <v>22.20598030090332</v>
       </c>
       <c r="C162" t="n">
         <v>26.60000038146973</v>
@@ -4619,7 +4631,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4648,11 +4660,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.75040245056152</v>
+        <v>25.75040054321289</v>
       </c>
       <c r="C164" t="n">
         <v>30.68000030517578</v>
@@ -4677,11 +4689,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.08974838256836</v>
+        <v>23.08975219726562</v>
       </c>
       <c r="C165" t="n">
         <v>27.51000022888184</v>
@@ -4706,11 +4718,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>24.64439010620117</v>
+        <v>24.6443977355957</v>
       </c>
       <c r="C166" t="n">
         <v>29.17000007629395</v>
@@ -4735,7 +4747,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4764,7 +4776,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4793,11 +4805,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>29.91821479797363</v>
+        <v>29.91821098327637</v>
       </c>
       <c r="C169" t="n">
         <v>35.22000122070312</v>
@@ -4822,11 +4834,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>27.88799095153809</v>
+        <v>27.88798332214355</v>
       </c>
       <c r="C170" t="n">
         <v>32.83000183105469</v>
@@ -4851,7 +4863,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4880,11 +4892,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>18.14924430847168</v>
+        <v>18.14925003051758</v>
       </c>
       <c r="C172" t="n">
         <v>21.22999954223633</v>
@@ -4909,11 +4921,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>20.56002616882324</v>
+        <v>20.56002807617188</v>
       </c>
       <c r="C173" t="n">
         <v>24.04999923706055</v>
@@ -4938,11 +4950,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>20.619873046875</v>
+        <v>20.6198673248291</v>
       </c>
       <c r="C174" t="n">
         <v>24.1200008392334</v>
@@ -4967,11 +4979,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>20.44516181945801</v>
+        <v>20.44515991210938</v>
       </c>
       <c r="C175" t="n">
         <v>23.75</v>
@@ -4996,11 +5008,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>21.41791534423828</v>
+        <v>21.41791915893555</v>
       </c>
       <c r="C176" t="n">
         <v>24.8799991607666</v>
@@ -5025,11 +5037,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>22.15824890136719</v>
+        <v>22.15825080871582</v>
       </c>
       <c r="C177" t="n">
         <v>25.73999977111816</v>
@@ -5054,11 +5066,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>20.88230895996094</v>
+        <v>20.8823070526123</v>
       </c>
       <c r="C178" t="n">
         <v>24.09000015258789</v>
@@ -5083,11 +5095,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>20.54424095153809</v>
+        <v>20.54423522949219</v>
       </c>
       <c r="C179" t="n">
         <v>23.70000076293945</v>
@@ -5112,11 +5124,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>24.41037368774414</v>
+        <v>24.41036796569824</v>
       </c>
       <c r="C180" t="n">
         <v>28.15999984741211</v>
@@ -5141,7 +5153,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5170,7 +5182,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5199,11 +5211,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>30.27573776245117</v>
+        <v>30.27573013305664</v>
       </c>
       <c r="C183" t="n">
         <v>34.70999908447266</v>
@@ -5228,11 +5240,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>33.9149055480957</v>
+        <v>33.91489791870117</v>
       </c>
       <c r="C184" t="n">
         <v>38.68999862670898</v>
@@ -5257,7 +5269,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5286,7 +5298,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5315,7 +5327,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5344,11 +5356,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>33.76717376708984</v>
+        <v>33.76717758178711</v>
       </c>
       <c r="C188" t="n">
         <v>38.36000061035156</v>
@@ -5373,11 +5385,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>36.75128936767578</v>
+        <v>36.75129699707031</v>
       </c>
       <c r="C189" t="n">
         <v>41.75</v>
@@ -5402,11 +5414,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>37.55896759033203</v>
+        <v>37.55897903442383</v>
       </c>
       <c r="C190" t="n">
         <v>42.45000076293945</v>
@@ -5431,11 +5443,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>42.27486038208008</v>
+        <v>42.27485656738281</v>
       </c>
       <c r="C191" t="n">
         <v>47.77999877929688</v>
@@ -5460,7 +5472,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5489,11 +5501,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>39.55339050292969</v>
+        <v>39.55340194702148</v>
       </c>
       <c r="C193" t="n">
         <v>44.4900016784668</v>
@@ -5518,11 +5530,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>41.02030563354492</v>
+        <v>41.02031707763672</v>
       </c>
       <c r="C194" t="n">
         <v>46.13999938964844</v>
@@ -5547,11 +5559,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>39.29557418823242</v>
+        <v>39.29557037353516</v>
       </c>
       <c r="C195" t="n">
         <v>44.20000076293945</v>
@@ -5576,11 +5588,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>36.82540893554688</v>
+        <v>36.82541275024414</v>
       </c>
       <c r="C196" t="n">
         <v>41.22000122070312</v>
@@ -5605,11 +5617,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>31.87605094909668</v>
+        <v>31.87605476379395</v>
       </c>
       <c r="C197" t="n">
         <v>35.68000030517578</v>
@@ -5634,11 +5646,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>33.2339973449707</v>
+        <v>33.23400115966797</v>
       </c>
       <c r="C198" t="n">
         <v>37.20000076293945</v>
@@ -5663,11 +5675,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>27.9713249206543</v>
+        <v>27.9713191986084</v>
       </c>
       <c r="C199" t="n">
         <v>31.1299991607666</v>
@@ -5692,7 +5704,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5721,11 +5733,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>30.19968223571777</v>
+        <v>30.19968795776367</v>
       </c>
       <c r="C201" t="n">
         <v>33.61000061035156</v>
@@ -5750,11 +5762,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>27.31447792053223</v>
+        <v>27.31447601318359</v>
       </c>
       <c r="C202" t="n">
         <v>30.20000076293945</v>
@@ -5779,11 +5791,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>32.59648132324219</v>
+        <v>32.59648513793945</v>
       </c>
       <c r="C203" t="n">
         <v>36.04000091552734</v>
@@ -5808,11 +5820,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>34.23353576660156</v>
+        <v>34.23353958129883</v>
       </c>
       <c r="C204" t="n">
         <v>37.84999847412109</v>
@@ -5837,11 +5849,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>30.13061332702637</v>
+        <v>30.13061141967773</v>
       </c>
       <c r="C205" t="n">
         <v>33.11999893188477</v>
@@ -5866,11 +5878,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>32.2775993347168</v>
+        <v>32.27759170532227</v>
       </c>
       <c r="C206" t="n">
         <v>35.47999954223633</v>
@@ -5895,11 +5907,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>31.20410346984863</v>
+        <v>31.2041072845459</v>
       </c>
       <c r="C207" t="n">
         <v>34.29999923706055</v>
@@ -5924,11 +5936,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>26.18733978271484</v>
+        <v>26.18733215332031</v>
       </c>
       <c r="C208" t="n">
         <v>28.60000038146973</v>
@@ -5953,11 +5965,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>26.80997276306152</v>
+        <v>26.80997467041016</v>
       </c>
       <c r="C209" t="n">
         <v>29.28000068664551</v>
@@ -5982,11 +5994,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.44566345214844</v>
+        <v>25.44566917419434</v>
       </c>
       <c r="C210" t="n">
         <v>27.79000091552734</v>
@@ -6011,7 +6023,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6040,7 +6052,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6069,7 +6081,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6098,11 +6110,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>25.48089218139648</v>
+        <v>25.48089027404785</v>
       </c>
       <c r="C214" t="n">
         <v>27.3799991607666</v>
@@ -6127,11 +6139,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>24.51302719116211</v>
+        <v>24.51303100585938</v>
       </c>
       <c r="C215" t="n">
         <v>26.34000015258789</v>
@@ -6156,7 +6168,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6185,11 +6197,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>31.58469772338867</v>
+        <v>31.5846996307373</v>
       </c>
       <c r="C217" t="n">
         <v>33.66999816894531</v>
@@ -6214,11 +6226,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>31.90364265441895</v>
+        <v>31.90363693237305</v>
       </c>
       <c r="C218" t="n">
         <v>34.0099983215332</v>
@@ -6243,7 +6255,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6272,7 +6284,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6301,11 +6313,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>34.96240615844727</v>
+        <v>34.96240997314453</v>
       </c>
       <c r="C221" t="n">
         <v>37.0099983215332</v>
@@ -6330,7 +6342,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6359,7 +6371,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6388,11 +6400,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>38.31144332885742</v>
+        <v>38.31143951416016</v>
       </c>
       <c r="C224" t="n">
         <v>40.31000137329102</v>
@@ -6417,11 +6429,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>38.72962188720703</v>
+        <v>38.7296257019043</v>
       </c>
       <c r="C225" t="n">
         <v>40.75</v>
@@ -6446,11 +6458,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>37.95854949951172</v>
+        <v>37.95854568481445</v>
       </c>
       <c r="C226" t="n">
         <v>39.68000030517578</v>
@@ -6475,7 +6487,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6504,7 +6516,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6533,7 +6545,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6562,11 +6574,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>44.53772354125977</v>
+        <v>44.53772735595703</v>
       </c>
       <c r="C230" t="n">
         <v>46.29999923706055</v>
@@ -6591,11 +6603,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>44.34534072875977</v>
+        <v>44.34534454345703</v>
       </c>
       <c r="C231" t="n">
         <v>46.09999847412109</v>
@@ -6620,11 +6632,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>40.39499282836914</v>
+        <v>40.39498901367188</v>
       </c>
       <c r="C232" t="n">
         <v>41.72999954223633</v>
@@ -6649,11 +6661,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>38.60417938232422</v>
+        <v>38.60418701171875</v>
       </c>
       <c r="C233" t="n">
         <v>39.88000106811523</v>
@@ -6678,7 +6690,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6707,11 +6719,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>46.07609939575195</v>
+        <v>46.07610321044922</v>
       </c>
       <c r="C235" t="n">
         <v>47.31999969482422</v>
@@ -6736,11 +6748,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>46.02740859985352</v>
+        <v>46.02741241455078</v>
       </c>
       <c r="C236" t="n">
         <v>47.27000045776367</v>
@@ -6765,7 +6777,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6794,11 +6806,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>50.51325988769531</v>
+        <v>50.51326370239258</v>
       </c>
       <c r="C238" t="n">
         <v>51.59000015258789</v>
@@ -6823,7 +6835,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6852,7 +6864,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6881,7 +6893,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6910,7 +6922,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6939,11 +6951,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>49.04354858398438</v>
+        <v>49.04354476928711</v>
       </c>
       <c r="C243" t="n">
         <v>49.83000183105469</v>
@@ -6968,7 +6980,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6997,11 +7009,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>52.9136962890625</v>
+        <v>52.91370010375977</v>
       </c>
       <c r="C245" t="n">
         <v>53.45999908447266</v>
@@ -7026,11 +7038,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>51.07270812988281</v>
+        <v>51.07270431518555</v>
       </c>
       <c r="C246" t="n">
         <v>51.59999847412109</v>
@@ -7055,7 +7067,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7084,7 +7096,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7113,7 +7125,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7142,32 +7154,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>56</v>
+        <v>56.02999877929688</v>
       </c>
       <c r="C250" t="n">
-        <v>56</v>
+        <v>56.02999877929688</v>
       </c>
       <c r="D250" t="n">
-        <v>602660400</v>
+        <v>643664500</v>
       </c>
       <c r="E250" t="n">
         <v>4.34</v>
       </c>
       <c r="F250" t="n">
-        <v>12.90322580645161</v>
+        <v>12.91013796757993</v>
       </c>
       <c r="G250" t="n">
         <v>6992748365</v>
       </c>
       <c r="H250" t="n">
-        <v>391593908440</v>
+        <v>391803682354.8802</v>
       </c>
       <c r="I250" t="n">
-        <v>0.08618362459836634</v>
+        <v>0.09204742776411919</v>
       </c>
     </row>
   </sheetData>
@@ -7199,75 +7211,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7303,13 +7315,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7345,13 +7357,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7387,13 +7399,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7429,13 +7441,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7471,13 +7483,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7513,13 +7525,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7555,13 +7567,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7597,13 +7609,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7630,7 +7642,7 @@
       <c r="I10" t="n">
         <v>-0.3699999999999999</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="K10" t="n">
@@ -7643,13 +7655,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7676,7 +7688,7 @@
       <c r="I11" t="n">
         <v>-0.4799999999999999</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K11" t="n">
@@ -7689,13 +7701,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7722,7 +7734,7 @@
       <c r="I12" t="n">
         <v>-1.65</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="K12" t="n">
@@ -7735,13 +7747,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7768,7 +7780,7 @@
       <c r="I13" t="n">
         <v>-0.32</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="K13" t="n">
@@ -7781,13 +7793,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7814,7 +7826,7 @@
       <c r="I14" t="n">
         <v>0.01000000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K14" t="n">
@@ -7827,13 +7839,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7860,7 +7872,7 @@
       <c r="I15" t="n">
         <v>-0.13</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K15" t="n">
@@ -7873,13 +7885,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7906,7 +7918,7 @@
       <c r="I16" t="n">
         <v>0.96</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="K16" t="n">
@@ -7919,13 +7931,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7952,7 +7964,7 @@
       <c r="I17" t="n">
         <v>0.4</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="K17" t="n">
@@ -7965,13 +7977,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7998,7 +8010,7 @@
       <c r="I18" t="n">
         <v>0.25</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="K18" t="n">
@@ -8011,13 +8023,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8044,7 +8056,7 @@
       <c r="I19" t="n">
         <v>0.3200000000000001</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K19" t="n">
@@ -8057,13 +8069,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8090,7 +8102,7 @@
       <c r="I20" t="n">
         <v>0.45</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="K20" t="n">
@@ -8103,13 +8115,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8136,7 +8148,7 @@
       <c r="I21" t="n">
         <v>0.65</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K21" t="n">
@@ -8149,13 +8161,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8182,7 +8194,7 @@
       <c r="I22" t="n">
         <v>0.8999999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K22" t="n">
@@ -8195,13 +8207,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8228,7 +8240,7 @@
       <c r="I23" t="n">
         <v>0.7499999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="K23" t="n">
@@ -8241,13 +8253,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8274,7 +8286,7 @@
       <c r="I24" t="n">
         <v>0.6199999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="K24" t="n">
@@ -8287,13 +8299,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8320,7 +8332,7 @@
       <c r="I25" t="n">
         <v>0.3799999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="K25" t="n">
@@ -8333,13 +8345,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8366,7 +8378,7 @@
       <c r="I26" t="n">
         <v>0.36</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K26" t="n">
@@ -8379,13 +8391,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8412,7 +8424,7 @@
       <c r="I27" t="n">
         <v>0.68</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K27" t="n">
@@ -8425,13 +8437,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8458,7 +8470,7 @@
       <c r="I28" t="n">
         <v>0.9400000000000001</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K28" t="n">
@@ -8471,13 +8483,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8504,7 +8516,7 @@
       <c r="I29" t="n">
         <v>1.35</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="K29" t="n">
@@ -8517,13 +8529,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8550,7 +8562,7 @@
       <c r="I30" t="n">
         <v>1.31</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K30" t="n">
@@ -8563,13 +8575,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8596,7 +8608,7 @@
       <c r="I31" t="n">
         <v>1.25</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="K31" t="n">
@@ -8609,13 +8621,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8642,7 +8654,7 @@
       <c r="I32" t="n">
         <v>1.16</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="K32" t="n">
@@ -8655,13 +8667,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8688,7 +8700,7 @@
       <c r="I33" t="n">
         <v>1.2</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="K33" t="n">
@@ -8701,13 +8713,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8734,7 +8746,7 @@
       <c r="I34" t="n">
         <v>1.5</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K34" t="n">
@@ -8747,13 +8759,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8780,7 +8792,7 @@
       <c r="I35" t="n">
         <v>1.7</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="K35" t="n">
@@ -8793,13 +8805,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8826,7 +8838,7 @@
       <c r="I36" t="n">
         <v>1.8</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="K36" t="n">
@@ -8839,13 +8851,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8872,7 +8884,7 @@
       <c r="I37" t="n">
         <v>1.87</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="K37" t="n">
@@ -8885,13 +8897,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8918,7 +8930,7 @@
       <c r="I38" t="n">
         <v>1.56</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K38" t="n">
@@ -8931,13 +8943,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8964,7 +8976,7 @@
       <c r="I39" t="n">
         <v>1.77</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="K39" t="n">
@@ -8977,13 +8989,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43311</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9010,7 +9022,7 @@
       <c r="I40" t="n">
         <v>1.94</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43311</v>
       </c>
       <c r="K40" t="n">
@@ -9023,13 +9035,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43402</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9056,7 +9068,7 @@
       <c r="I41" t="n">
         <v>2.12</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43402</v>
       </c>
       <c r="K41" t="n">
@@ -9069,13 +9081,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9102,7 +9114,7 @@
       <c r="I42" t="n">
         <v>2.61</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="K42" t="n">
@@ -9115,13 +9127,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9148,7 +9160,7 @@
       <c r="I43" t="n">
         <v>2.69</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="K43" t="n">
@@ -9161,13 +9173,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43675</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9194,7 +9206,7 @@
       <c r="I44" t="n">
         <v>2.8</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43675</v>
       </c>
       <c r="K44" t="n">
@@ -9207,13 +9219,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43766</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9240,7 +9252,7 @@
       <c r="I45" t="n">
         <v>2.7</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43766</v>
       </c>
       <c r="K45" t="n">
@@ -9253,13 +9265,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9286,7 +9298,7 @@
       <c r="I46" t="n">
         <v>2.75</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="K46" t="n">
@@ -9299,13 +9311,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9332,7 +9344,7 @@
       <c r="I47" t="n">
         <v>2.45</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K47" t="n">
@@ -9345,13 +9357,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9378,7 +9390,7 @@
       <c r="I48" t="n">
         <v>2.08</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K48" t="n">
@@ -9391,13 +9403,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9424,7 +9436,7 @@
       <c r="I49" t="n">
         <v>2.03</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K49" t="n">
@@ -9437,13 +9449,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9470,7 +9482,7 @@
       <c r="I50" t="n">
         <v>1.87</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="K50" t="n">
@@ -9483,13 +9495,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9516,7 +9528,7 @@
       <c r="I51" t="n">
         <v>2.33</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="K51" t="n">
@@ -9529,13 +9541,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9562,7 +9574,7 @@
       <c r="I52" t="n">
         <v>2.99</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K52" t="n">
@@ -9575,13 +9587,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9608,7 +9620,7 @@
       <c r="I53" t="n">
         <v>3.330000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K53" t="n">
@@ -9621,13 +9633,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9654,7 +9666,7 @@
       <c r="I54" t="n">
         <v>3.57</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K54" t="n">
@@ -9667,13 +9679,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9700,7 +9712,7 @@
       <c r="I55" t="n">
         <v>3.51</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K55" t="n">
@@ -9713,13 +9725,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9746,7 +9758,7 @@
       <c r="I56" t="n">
         <v>3.21</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="K56" t="n">
@@ -9759,13 +9771,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9792,7 +9804,7 @@
       <c r="I57" t="n">
         <v>3.169999999999999</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="K57" t="n">
@@ -9805,13 +9817,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9838,7 +9850,7 @@
       <c r="I58" t="n">
         <v>3.19</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="K58" t="n">
@@ -9851,13 +9863,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9884,7 +9896,7 @@
       <c r="I59" t="n">
         <v>3.33</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="K59" t="n">
@@ -9897,13 +9909,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9930,7 +9942,7 @@
       <c r="I60" t="n">
         <v>3.48</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="K60" t="n">
@@ -9943,13 +9955,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9976,7 +9988,7 @@
       <c r="I61" t="n">
         <v>3.57</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="K61" t="n">
@@ -9989,13 +10001,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10022,7 +10034,7 @@
       <c r="I62" t="n">
         <v>3.080000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K62" t="n">
@@ -10035,13 +10047,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10068,7 +10080,7 @@
       <c r="I63" t="n">
         <v>2.9</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="K63" t="n">
@@ -10081,13 +10093,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10114,7 +10126,7 @@
       <c r="I64" t="n">
         <v>2.850000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="K64" t="n">
@@ -10127,13 +10139,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10160,7 +10172,7 @@
       <c r="I65" t="n">
         <v>2.76</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="K65" t="n">
@@ -10173,13 +10185,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10206,7 +10218,7 @@
       <c r="I66" t="n">
         <v>3.21</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="K66" t="n">
@@ -10219,13 +10231,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10252,7 +10264,7 @@
       <c r="I67" t="n">
         <v>3.35</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="K67" t="n">
@@ -10265,13 +10277,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10298,7 +10310,7 @@
       <c r="I68" t="n">
         <v>3.41</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="K68" t="n">
@@ -10311,13 +10323,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10344,7 +10356,7 @@
       <c r="I69" t="n">
         <v>3.66</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K69" t="n">
@@ -10357,13 +10369,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10390,7 +10402,7 @@
       <c r="I70" t="n">
         <v>3.81</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K70" t="n">
@@ -10403,13 +10415,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10436,7 +10448,7 @@
       <c r="I71" t="n">
         <v>4.02</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K71" t="n">
@@ -10449,13 +10461,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10482,7 +10494,7 @@
       <c r="I72" t="n">
         <v>4.34</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K72" t="n">
@@ -10519,52 +10531,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40032</v>
       </c>
       <c r="C2" t="n">
@@ -10593,10 +10605,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10625,10 +10637,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40233</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10657,10 +10669,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40305</v>
       </c>
       <c r="C5" t="n">
@@ -10689,10 +10701,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40396</v>
       </c>
       <c r="C6" t="n">
@@ -10721,10 +10733,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10753,10 +10765,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40589</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40599</v>
       </c>
       <c r="C8" t="n">
@@ -10785,10 +10797,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10817,10 +10829,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40759</v>
       </c>
       <c r="C10" t="n">
@@ -10849,10 +10861,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40850</v>
       </c>
       <c r="C11" t="n">
@@ -10881,10 +10893,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40956</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C12" t="n">
@@ -10913,10 +10925,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -10945,10 +10957,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41123</v>
       </c>
       <c r="C14" t="n">
@@ -10977,10 +10989,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41215</v>
       </c>
       <c r="C15" t="n">
@@ -11009,10 +11021,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41330</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="C16" t="n">
@@ -11041,10 +11053,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41397</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C17" t="n">
@@ -11073,10 +11085,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="C18" t="n">
@@ -11105,10 +11117,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41576</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C19" t="n">
@@ -11137,10 +11149,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41694</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C20" t="n">
@@ -11169,10 +11181,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="C21" t="n">
@@ -11201,10 +11213,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41848</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41849</v>
       </c>
       <c r="C22" t="n">
@@ -11233,10 +11245,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41948</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41949</v>
       </c>
       <c r="C23" t="n">
@@ -11265,10 +11277,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42059</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C24" t="n">
@@ -11297,10 +11309,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42122</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C25" t="n">
@@ -11329,10 +11341,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42213</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C26" t="n">
@@ -11361,10 +11373,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42306</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42307</v>
       </c>
       <c r="C27" t="n">
@@ -11393,10 +11405,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42423</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C28" t="n">
@@ -11425,10 +11437,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42492</v>
       </c>
       <c r="C29" t="n">
@@ -11457,10 +11469,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42583</v>
       </c>
       <c r="C30" t="n">
@@ -11489,10 +11501,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42675</v>
       </c>
       <c r="C31" t="n">
@@ -11521,10 +11533,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42788</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11553,10 +11565,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42857</v>
       </c>
       <c r="C33" t="n">
@@ -11585,10 +11597,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42944</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="C34" t="n">
@@ -11617,10 +11629,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43035</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43038</v>
       </c>
       <c r="C35" t="n">
@@ -11649,10 +11661,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43152</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C36" t="n">
@@ -11681,10 +11693,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="C37" t="n">
@@ -11713,10 +11725,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43308</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43311</v>
       </c>
       <c r="C38" t="n">
@@ -11745,10 +11757,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43402</v>
       </c>
       <c r="C39" t="n">
@@ -11777,10 +11789,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43521</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43522</v>
       </c>
       <c r="C40" t="n">
@@ -11809,10 +11821,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43580</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43581</v>
       </c>
       <c r="C41" t="n">
@@ -11841,10 +11853,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43672</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43675</v>
       </c>
       <c r="C42" t="n">
@@ -11873,10 +11885,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43763</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43766</v>
       </c>
       <c r="C43" t="n">
@@ -11905,10 +11917,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43879</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43880</v>
       </c>
       <c r="C44" t="n">
@@ -11937,10 +11949,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -11969,10 +11981,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44041</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -12001,10 +12013,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44133</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C47" t="n">
@@ -12033,10 +12045,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44250</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44251</v>
       </c>
       <c r="C48" t="n">
@@ -12065,10 +12077,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44314</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44315</v>
       </c>
       <c r="C49" t="n">
@@ -12097,10 +12109,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44406</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C50" t="n">
@@ -12129,10 +12141,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44497</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C51" t="n">
@@ -12161,10 +12173,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C52" t="n">
@@ -12193,10 +12205,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44679</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12225,10 +12237,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44770</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44771</v>
       </c>
       <c r="C54" t="n">
@@ -12257,10 +12269,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44861</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44862</v>
       </c>
       <c r="C55" t="n">
@@ -12289,10 +12301,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44978</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44979</v>
       </c>
       <c r="C56" t="n">
@@ -12321,10 +12333,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="C57" t="n">
@@ -12353,10 +12365,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45135</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="C58" t="n">
@@ -12385,10 +12397,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="C59" t="n">
@@ -12417,10 +12429,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C60" t="n">
@@ -12449,10 +12461,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="C61" t="n">
@@ -12481,10 +12493,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45502</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45503</v>
       </c>
       <c r="C62" t="n">
@@ -12513,10 +12525,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45593</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45594</v>
       </c>
       <c r="C63" t="n">
@@ -12545,10 +12557,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45712</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C64" t="n">
@@ -12577,10 +12589,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45776</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="C65" t="n">
@@ -12609,10 +12621,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45868</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C66" t="n">
@@ -12641,10 +12653,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C67" t="n">
@@ -12673,10 +12685,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46077</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C68" t="n">
@@ -12705,10 +12717,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12737,10 +12749,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46233</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C70" t="n">
@@ -12787,12 +12799,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/BAC.xlsx
+++ b/salidas/empresas/BAC.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>28.34963989257812</v>
+        <v>28.34963607788086</v>
       </c>
       <c r="C2" t="n">
         <v>44.22999954223633</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>29.38799858093262</v>
+        <v>29.38800621032715</v>
       </c>
       <c r="C3" t="n">
         <v>45.84999847412109</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>29.51113128662109</v>
+        <v>29.51113510131836</v>
       </c>
       <c r="C4" t="n">
         <v>45.54000091552734</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>32.3494873046875</v>
+        <v>32.3494758605957</v>
       </c>
       <c r="C5" t="n">
         <v>49.91999816894531</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>31.68984985351562</v>
+        <v>31.68983840942383</v>
       </c>
       <c r="C6" t="n">
         <v>48.40000152587891</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>31.49341201782227</v>
+        <v>31.4934253692627</v>
       </c>
       <c r="C7" t="n">
         <v>48.09999847412109</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>33.73920440673828</v>
+        <v>33.73921203613281</v>
       </c>
       <c r="C8" t="n">
         <v>51.52999877929688</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>34.06473922729492</v>
+        <v>34.06474304199219</v>
       </c>
       <c r="C9" t="n">
         <v>51.47000122070312</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>35.4545783996582</v>
+        <v>35.45458984375</v>
       </c>
       <c r="C10" t="n">
         <v>53.56999969482422</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>36.01150512695312</v>
+        <v>36.01151657104492</v>
       </c>
       <c r="C12" t="n">
         <v>53.84999847412109</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>35.16220855712891</v>
+        <v>35.16220092773438</v>
       </c>
       <c r="C14" t="n">
         <v>52.58000183105469</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>34.37081146240234</v>
+        <v>34.37080764770508</v>
       </c>
       <c r="C15" t="n">
         <v>50.83000183105469</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>34.41813659667969</v>
+        <v>34.41814804077148</v>
       </c>
       <c r="C17" t="n">
         <v>50.90000152587891</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>33.42464828491211</v>
+        <v>33.4246711730957</v>
       </c>
       <c r="C19" t="n">
         <v>48.88999938964844</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>32.41965103149414</v>
+        <v>32.41967391967773</v>
       </c>
       <c r="C20" t="n">
         <v>47.41999816894531</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>34.80419540405273</v>
+        <v>34.8041877746582</v>
       </c>
       <c r="C22" t="n">
         <v>50.27000045776367</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>33.42640686035156</v>
+        <v>33.42642593383789</v>
       </c>
       <c r="C23" t="n">
         <v>48.27999877929688</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>31.9378833770752</v>
+        <v>31.93788909912109</v>
       </c>
       <c r="C24" t="n">
         <v>46.13000106811523</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>28.98101234436035</v>
+        <v>28.98100852966309</v>
       </c>
       <c r="C25" t="n">
         <v>41.2599983215332</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>31.01094818115234</v>
+        <v>31.01095008850098</v>
       </c>
       <c r="C26" t="n">
         <v>44.15000152587891</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>27.91336822509766</v>
+        <v>27.91336059570312</v>
       </c>
       <c r="C27" t="n">
         <v>39.7400016784668</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>27.07479095458984</v>
+        <v>27.07479858398438</v>
       </c>
       <c r="C28" t="n">
         <v>37.90999984741211</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>26.81054306030273</v>
+        <v>26.81054878234863</v>
       </c>
       <c r="C29" t="n">
         <v>37.54000091552734</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>24.28946304321289</v>
+        <v>24.28946685791016</v>
       </c>
       <c r="C30" t="n">
         <v>34.0099983215332</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>17.3815803527832</v>
+        <v>17.38158798217773</v>
       </c>
       <c r="C31" t="n">
         <v>23.8700008392334</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>23.95701789855957</v>
+        <v>23.95702171325684</v>
       </c>
       <c r="C32" t="n">
         <v>32.90000152587891</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>22.67541694641113</v>
+        <v>22.67542839050293</v>
       </c>
       <c r="C33" t="n">
         <v>31.13999938964844</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>25.9960823059082</v>
+        <v>25.99608421325684</v>
       </c>
       <c r="C34" t="n">
         <v>35</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>12.06960391998291</v>
+        <v>12.06960773468018</v>
       </c>
       <c r="C36" t="n">
         <v>16.25</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>10.69603538513184</v>
+        <v>10.69603252410889</v>
       </c>
       <c r="C37" t="n">
         <v>14.07999992370605</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>4.998574733734131</v>
+        <v>4.998573780059814</v>
       </c>
       <c r="C38" t="n">
         <v>6.579999923706055</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>6.802414417266846</v>
+        <v>6.802413940429688</v>
       </c>
       <c r="C41" t="n">
         <v>8.930000305175781</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>8.584905624389648</v>
+        <v>8.584909439086914</v>
       </c>
       <c r="C42" t="n">
         <v>11.27000045776367</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>10.06390190124512</v>
+        <v>10.06389808654785</v>
       </c>
       <c r="C43" t="n">
         <v>13.19999980926514</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>11.27614212036133</v>
+        <v>11.27614498138428</v>
       </c>
       <c r="C44" t="n">
         <v>14.78999996185303</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>13.41090965270996</v>
+        <v>13.41090774536133</v>
       </c>
       <c r="C45" t="n">
         <v>17.59000015258789</v>
@@ -1340,7 +1340,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>12.90792942047119</v>
+        <v>12.90793228149414</v>
       </c>
       <c r="C46" t="n">
         <v>16.92000007629395</v>
@@ -1365,7 +1365,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>11.1227970123291</v>
+        <v>11.12279605865479</v>
       </c>
       <c r="C47" t="n">
         <v>14.57999992370605</v>
@@ -1390,7 +1390,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>12.09165191650391</v>
+        <v>12.09165382385254</v>
       </c>
       <c r="C48" t="n">
         <v>15.85000038146973</v>
@@ -1440,7 +1440,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>11.58780670166016</v>
+        <v>11.58780956268311</v>
       </c>
       <c r="C50" t="n">
         <v>15.18000030517578</v>
@@ -1465,7 +1465,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>12.7175817489624</v>
+        <v>12.71758460998535</v>
       </c>
       <c r="C51" t="n">
         <v>16.65999984741211</v>
@@ -1515,7 +1515,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>13.61898899078369</v>
+        <v>13.61899566650391</v>
       </c>
       <c r="C53" t="n">
         <v>17.82999992370605</v>
@@ -1540,7 +1540,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>12.02259349822998</v>
+        <v>12.02259731292725</v>
       </c>
       <c r="C54" t="n">
         <v>15.73999977111816</v>
@@ -1565,7 +1565,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>10.98327159881592</v>
+        <v>10.98326969146729</v>
       </c>
       <c r="C55" t="n">
         <v>14.36999988555908</v>
@@ -1590,7 +1590,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>10.73104476928711</v>
+        <v>10.73104667663574</v>
       </c>
       <c r="C56" t="n">
         <v>14.03999996185303</v>
@@ -1615,7 +1615,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>9.523422241210938</v>
+        <v>9.523421287536621</v>
       </c>
       <c r="C57" t="n">
         <v>12.46000003814697</v>
@@ -1640,7 +1640,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>10.02062797546387</v>
+        <v>10.02062702178955</v>
       </c>
       <c r="C58" t="n">
         <v>13.10000038146973</v>
@@ -1665,7 +1665,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>8.75848388671875</v>
+        <v>8.758486747741699</v>
       </c>
       <c r="C59" t="n">
         <v>11.44999980926514</v>
@@ -1690,7 +1690,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>8.376023292541504</v>
+        <v>8.376014709472656</v>
       </c>
       <c r="C60" t="n">
         <v>10.94999980926514</v>
@@ -1740,7 +1740,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>10.51213455200195</v>
+        <v>10.51213359832764</v>
       </c>
       <c r="C62" t="n">
         <v>13.72999954223633</v>
@@ -1765,7 +1765,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>10.94089031219482</v>
+        <v>10.94089317321777</v>
       </c>
       <c r="C63" t="n">
         <v>14.28999996185303</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>9.408720016479492</v>
+        <v>9.408724784851074</v>
       </c>
       <c r="C65" t="n">
         <v>12.27999973297119</v>
@@ -1846,7 +1846,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>9.002642631530762</v>
+        <v>9.002647399902344</v>
       </c>
       <c r="C66" t="n">
         <v>11.75</v>
@@ -1900,7 +1900,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>7.445969581604004</v>
+        <v>7.445969104766846</v>
       </c>
       <c r="C68" t="n">
         <v>9.710000038146973</v>
@@ -1927,7 +1927,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>6.272770404815674</v>
+        <v>6.272769927978516</v>
       </c>
       <c r="C69" t="n">
         <v>8.170000076293945</v>
@@ -1954,7 +1954,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>4.698817729949951</v>
+        <v>4.698818683624268</v>
       </c>
       <c r="C70" t="n">
         <v>6.119999885559082</v>
@@ -1981,7 +1981,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>5.243941783905029</v>
+        <v>5.243942737579346</v>
       </c>
       <c r="C71" t="n">
         <v>6.829999923706055</v>
@@ -2008,7 +2008,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>4.184967041015625</v>
+        <v>4.184964179992676</v>
       </c>
       <c r="C72" t="n">
         <v>5.440000057220459</v>
@@ -2035,7 +2035,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>4.277278900146484</v>
+        <v>4.277279853820801</v>
       </c>
       <c r="C73" t="n">
         <v>5.559999942779541</v>
@@ -2062,7 +2062,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>5.485074043273926</v>
+        <v>5.485073089599609</v>
       </c>
       <c r="C74" t="n">
         <v>7.130000114440918</v>
@@ -2089,7 +2089,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>6.138842582702637</v>
+        <v>6.138842105865479</v>
       </c>
       <c r="C75" t="n">
         <v>7.96999979019165</v>
@@ -2147,7 +2147,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>6.246677398681641</v>
+        <v>6.246674537658691</v>
       </c>
       <c r="C77" t="n">
         <v>8.109999656677246</v>
@@ -2176,7 +2176,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>5.668910980224609</v>
+        <v>5.668909549713135</v>
       </c>
       <c r="C78" t="n">
         <v>7.349999904632568</v>
@@ -2203,7 +2203,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>6.309073448181152</v>
+        <v>6.309074401855469</v>
       </c>
       <c r="C79" t="n">
         <v>8.180000305175781</v>
@@ -2230,7 +2230,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>5.661196708679199</v>
+        <v>5.661198139190674</v>
       </c>
       <c r="C80" t="n">
         <v>7.340000152587891</v>
@@ -2257,7 +2257,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>6.162529945373535</v>
+        <v>6.162529468536377</v>
       </c>
       <c r="C81" t="n">
         <v>7.989999771118164</v>
@@ -2315,7 +2315,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>7.197329044342041</v>
+        <v>7.197328090667725</v>
       </c>
       <c r="C83" t="n">
         <v>9.319999694824219</v>
@@ -2344,7 +2344,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>7.61434268951416</v>
+        <v>7.614343643188477</v>
       </c>
       <c r="C84" t="n">
         <v>9.859999656677246</v>
@@ -2402,7 +2402,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>8.750653266906738</v>
+        <v>8.750652313232422</v>
       </c>
       <c r="C86" t="n">
         <v>11.31999969482422</v>
@@ -2431,7 +2431,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>8.688886642456055</v>
+        <v>8.688883781433105</v>
       </c>
       <c r="C87" t="n">
         <v>11.22999954223633</v>
@@ -2460,7 +2460,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>9.423922538757324</v>
+        <v>9.423918724060059</v>
       </c>
       <c r="C88" t="n">
         <v>12.18000030517578</v>
@@ -2489,7 +2489,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>9.524506568908691</v>
+        <v>9.524504661560059</v>
       </c>
       <c r="C89" t="n">
         <v>12.3100004196167</v>
@@ -2518,7 +2518,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>10.56902694702148</v>
+        <v>10.5690279006958</v>
       </c>
       <c r="C90" t="n">
         <v>13.65999984741211</v>
@@ -2547,7 +2547,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>9.95750617980957</v>
+        <v>9.957503318786621</v>
       </c>
       <c r="C91" t="n">
         <v>12.85999965667725</v>
@@ -2576,7 +2576,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>11.30478763580322</v>
+        <v>11.30478858947754</v>
       </c>
       <c r="C92" t="n">
         <v>14.60000038146973</v>
@@ -2605,7 +2605,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>10.9331226348877</v>
+        <v>10.93312454223633</v>
       </c>
       <c r="C93" t="n">
         <v>14.11999988555908</v>
@@ -2634,7 +2634,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>10.69285106658936</v>
+        <v>10.69285011291504</v>
       </c>
       <c r="C94" t="n">
         <v>13.80000019073486</v>
@@ -2663,7 +2663,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>10.82457637786865</v>
+        <v>10.82457447052002</v>
       </c>
       <c r="C95" t="n">
         <v>13.97000026702881</v>
@@ -2692,7 +2692,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>12.25803565979004</v>
+        <v>12.25803470611572</v>
       </c>
       <c r="C96" t="n">
         <v>15.81999969482422</v>
@@ -2721,7 +2721,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>12.07209300994873</v>
+        <v>12.07208919525146</v>
       </c>
       <c r="C97" t="n">
         <v>15.56999969482422</v>
@@ -2779,7 +2779,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>12.81642532348633</v>
+        <v>12.81642436981201</v>
       </c>
       <c r="C99" t="n">
         <v>16.53000068664551</v>
@@ -2808,7 +2808,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>13.34387493133545</v>
+        <v>13.34388256072998</v>
       </c>
       <c r="C100" t="n">
         <v>17.20000076293945</v>
@@ -2837,7 +2837,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>11.74571514129639</v>
+        <v>11.74571895599365</v>
       </c>
       <c r="C101" t="n">
         <v>15.14000034332275</v>
@@ -2866,7 +2866,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>11.74571514129639</v>
+        <v>11.74571895599365</v>
       </c>
       <c r="C102" t="n">
         <v>15.14000034332275</v>
@@ -2924,7 +2924,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>11.83866500854492</v>
+        <v>11.83866691589355</v>
       </c>
       <c r="C104" t="n">
         <v>15.25</v>
@@ -2953,7 +2953,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>12.49076461791992</v>
+        <v>12.49076271057129</v>
       </c>
       <c r="C105" t="n">
         <v>16.09000015258789</v>
@@ -2982,7 +2982,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>13.27681827545166</v>
+        <v>13.27682113647461</v>
       </c>
       <c r="C106" t="n">
         <v>17.04999923706055</v>
@@ -3011,7 +3011,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>13.362473487854</v>
+        <v>13.36247825622559</v>
       </c>
       <c r="C107" t="n">
         <v>17.15999984741211</v>
@@ -3040,7 +3040,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>13.26903820037842</v>
+        <v>13.2690315246582</v>
       </c>
       <c r="C108" t="n">
         <v>17.04000091552734</v>
@@ -3069,7 +3069,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>13.97165870666504</v>
+        <v>13.97166156768799</v>
       </c>
       <c r="C109" t="n">
         <v>17.88999938964844</v>
@@ -3098,7 +3098,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>11.83178520202637</v>
+        <v>11.83178901672363</v>
       </c>
       <c r="C110" t="n">
         <v>15.14999961853027</v>
@@ -3127,7 +3127,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>12.34723281860352</v>
+        <v>12.34723091125488</v>
       </c>
       <c r="C111" t="n">
         <v>15.8100004196167</v>
@@ -3156,7 +3156,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>12.05680370330811</v>
+        <v>12.05680561065674</v>
       </c>
       <c r="C112" t="n">
         <v>15.39000034332275</v>
@@ -3185,7 +3185,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>12.47984886169434</v>
+        <v>12.4798526763916</v>
       </c>
       <c r="C113" t="n">
         <v>15.93000030517578</v>
@@ -3214,7 +3214,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>12.92640209197998</v>
+        <v>12.92640018463135</v>
       </c>
       <c r="C114" t="n">
         <v>16.5</v>
@@ -3243,7 +3243,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>13.3737678527832</v>
+        <v>13.37377071380615</v>
       </c>
       <c r="C115" t="n">
         <v>17.02000045776367</v>
@@ -3272,7 +3272,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>14.04952621459961</v>
+        <v>14.04952812194824</v>
       </c>
       <c r="C116" t="n">
         <v>17.8799991607666</v>
@@ -3301,7 +3301,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>12.83944988250732</v>
+        <v>12.83944797515869</v>
       </c>
       <c r="C117" t="n">
         <v>16.34000015258789</v>
@@ -3330,7 +3330,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>12.2816801071167</v>
+        <v>12.28167629241943</v>
       </c>
       <c r="C118" t="n">
         <v>15.57999992370605</v>
@@ -3359,7 +3359,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>13.22763729095459</v>
+        <v>13.22763538360596</v>
       </c>
       <c r="C119" t="n">
         <v>16.78000068664551</v>
@@ -3388,7 +3388,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>13.74002838134766</v>
+        <v>13.74003314971924</v>
       </c>
       <c r="C120" t="n">
         <v>17.43000030517578</v>
@@ -3417,7 +3417,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>13.30440139770508</v>
+        <v>13.30439949035645</v>
       </c>
       <c r="C121" t="n">
         <v>16.82999992370605</v>
@@ -3446,7 +3446,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>11.17791271209717</v>
+        <v>11.17791080474854</v>
       </c>
       <c r="C122" t="n">
         <v>14.14000034332275</v>
@@ -3475,7 +3475,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>9.897273063659668</v>
+        <v>9.897272109985352</v>
       </c>
       <c r="C123" t="n">
         <v>12.52000045776367</v>
@@ -3504,7 +3504,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>10.7284631729126</v>
+        <v>10.72846221923828</v>
       </c>
       <c r="C124" t="n">
         <v>13.52000045776367</v>
@@ -3533,7 +3533,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>11.55372714996338</v>
+        <v>11.55372524261475</v>
       </c>
       <c r="C125" t="n">
         <v>14.5600004196167</v>
@@ -3562,7 +3562,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>11.73623371124268</v>
+        <v>11.73623752593994</v>
       </c>
       <c r="C126" t="n">
         <v>14.78999996185303</v>
@@ -3591,7 +3591,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>10.56579780578613</v>
+        <v>10.56579971313477</v>
       </c>
       <c r="C127" t="n">
         <v>13.27000045776367</v>
@@ -3649,7 +3649,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>12.91074848175049</v>
+        <v>12.91075229644775</v>
       </c>
       <c r="C129" t="n">
         <v>16.13999938964844</v>
@@ -3678,7 +3678,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>12.51878452301025</v>
+        <v>12.51878547668457</v>
       </c>
       <c r="C130" t="n">
         <v>15.64999961853027</v>
@@ -3707,7 +3707,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>13.19872379302979</v>
+        <v>13.1987190246582</v>
       </c>
       <c r="C131" t="n">
         <v>16.5</v>
@@ -3765,7 +3765,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>17.74387359619141</v>
+        <v>17.74387550354004</v>
       </c>
       <c r="C133" t="n">
         <v>22.10000038146973</v>
@@ -3794,7 +3794,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>18.17743492126465</v>
+        <v>18.17743873596191</v>
       </c>
       <c r="C134" t="n">
         <v>22.63999938964844</v>
@@ -3823,7 +3823,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>19.8153247833252</v>
+        <v>19.81533241271973</v>
       </c>
       <c r="C135" t="n">
         <v>24.68000030517578</v>
@@ -3852,7 +3852,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>18.99790954589844</v>
+        <v>18.99791526794434</v>
       </c>
       <c r="C136" t="n">
         <v>23.59000015258789</v>
@@ -3881,7 +3881,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>18.79657745361328</v>
+        <v>18.79657363891602</v>
       </c>
       <c r="C137" t="n">
         <v>23.34000015258789</v>
@@ -3910,7 +3910,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>18.10688972473145</v>
+        <v>18.10689544677734</v>
       </c>
       <c r="C138" t="n">
         <v>22.40999984741211</v>
@@ -3968,7 +3968,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>19.4885425567627</v>
+        <v>19.48853874206543</v>
       </c>
       <c r="C140" t="n">
         <v>24.1200008392334</v>
@@ -3997,7 +3997,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>19.40143966674805</v>
+        <v>19.40143203735352</v>
       </c>
       <c r="C141" t="n">
         <v>23.88999938964844</v>
@@ -4026,7 +4026,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>20.57900810241699</v>
+        <v>20.57900428771973</v>
       </c>
       <c r="C142" t="n">
         <v>25.34000015258789</v>
@@ -4055,7 +4055,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>22.24385070800781</v>
+        <v>22.24384117126465</v>
       </c>
       <c r="C143" t="n">
         <v>27.38999938964844</v>
@@ -4084,7 +4084,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>22.97478103637695</v>
+        <v>22.97478294372559</v>
       </c>
       <c r="C144" t="n">
         <v>28.17000007629395</v>
@@ -4113,7 +4113,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>24.07581329345703</v>
+        <v>24.07580947875977</v>
       </c>
       <c r="C145" t="n">
         <v>29.52000045776367</v>
@@ -4171,7 +4171,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>26.17999649047852</v>
+        <v>26.18000030517578</v>
       </c>
       <c r="C147" t="n">
         <v>32.09999847412109</v>
@@ -4258,7 +4258,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>23.87033462524414</v>
+        <v>23.87034225463867</v>
       </c>
       <c r="C150" t="n">
         <v>29.04000091552734</v>
@@ -4287,7 +4287,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>23.17165374755859</v>
+        <v>23.17165565490723</v>
       </c>
       <c r="C151" t="n">
         <v>28.19000053405762</v>
@@ -4316,7 +4316,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>25.38278579711914</v>
+        <v>25.38278770446777</v>
       </c>
       <c r="C152" t="n">
         <v>30.8799991607666</v>
@@ -4345,7 +4345,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>25.42388725280762</v>
+        <v>25.42388916015625</v>
       </c>
       <c r="C153" t="n">
         <v>30.93000030517578</v>
@@ -4374,7 +4374,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>24.33263397216797</v>
+        <v>24.33263206481934</v>
       </c>
       <c r="C154" t="n">
         <v>29.45999908447266</v>
@@ -4403,7 +4403,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>22.71376037597656</v>
+        <v>22.7137622833252</v>
       </c>
       <c r="C155" t="n">
         <v>27.5</v>
@@ -4432,7 +4432,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>23.45711708068848</v>
+        <v>23.45711517333984</v>
       </c>
       <c r="C156" t="n">
         <v>28.39999961853027</v>
@@ -4461,7 +4461,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>20.46525764465332</v>
+        <v>20.46526145935059</v>
       </c>
       <c r="C157" t="n">
         <v>24.63999938964844</v>
@@ -4490,7 +4490,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>23.64634704589844</v>
+        <v>23.6463508605957</v>
       </c>
       <c r="C158" t="n">
         <v>28.46999931335449</v>
@@ -4519,7 +4519,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>24.27630996704102</v>
+        <v>24.27631187438965</v>
       </c>
       <c r="C159" t="n">
         <v>29.07999992370605</v>
@@ -4548,7 +4548,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>23.03244400024414</v>
+        <v>23.03244590759277</v>
       </c>
       <c r="C160" t="n">
         <v>27.59000015258789</v>
@@ -4606,7 +4606,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>22.20598030090332</v>
+        <v>22.20598220825195</v>
       </c>
       <c r="C162" t="n">
         <v>26.60000038146973</v>
@@ -4635,7 +4635,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>24.34034156799316</v>
+        <v>24.34034538269043</v>
       </c>
       <c r="C163" t="n">
         <v>29</v>
@@ -4664,7 +4664,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>25.75040054321289</v>
+        <v>25.75040435791016</v>
       </c>
       <c r="C164" t="n">
         <v>30.68000030517578</v>
@@ -4693,7 +4693,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>23.08975219726562</v>
+        <v>23.08975791931152</v>
       </c>
       <c r="C165" t="n">
         <v>27.51000022888184</v>
@@ -4722,7 +4722,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>24.6443977355957</v>
+        <v>24.64439582824707</v>
       </c>
       <c r="C166" t="n">
         <v>29.17000007629395</v>
@@ -4751,7 +4751,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>26.4185848236084</v>
+        <v>26.41858863830566</v>
       </c>
       <c r="C167" t="n">
         <v>31.27000045776367</v>
@@ -4780,7 +4780,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>28.15054130554199</v>
+        <v>28.15053749084473</v>
       </c>
       <c r="C168" t="n">
         <v>33.31999969482422</v>
@@ -4809,7 +4809,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>29.91821098327637</v>
+        <v>29.91821479797363</v>
       </c>
       <c r="C169" t="n">
         <v>35.22000122070312</v>
@@ -4838,7 +4838,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>27.88798332214355</v>
+        <v>27.88799476623535</v>
       </c>
       <c r="C170" t="n">
         <v>32.83000183105469</v>
@@ -4867,7 +4867,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>24.20979690551758</v>
+        <v>24.20979499816895</v>
       </c>
       <c r="C171" t="n">
         <v>28.5</v>
@@ -4896,7 +4896,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>18.14925003051758</v>
+        <v>18.14924812316895</v>
       </c>
       <c r="C172" t="n">
         <v>21.22999954223633</v>
@@ -4954,7 +4954,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>20.6198673248291</v>
+        <v>20.61986923217773</v>
       </c>
       <c r="C174" t="n">
         <v>24.1200008392334</v>
@@ -5012,7 +5012,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>21.41791915893555</v>
+        <v>21.41792297363281</v>
       </c>
       <c r="C176" t="n">
         <v>24.8799991607666</v>
@@ -5041,7 +5041,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>22.15825080871582</v>
+        <v>22.15824699401855</v>
       </c>
       <c r="C177" t="n">
         <v>25.73999977111816</v>
@@ -5070,7 +5070,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>20.8823070526123</v>
+        <v>20.88230514526367</v>
       </c>
       <c r="C178" t="n">
         <v>24.09000015258789</v>
@@ -5099,7 +5099,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>20.54423522949219</v>
+        <v>20.54423713684082</v>
       </c>
       <c r="C179" t="n">
         <v>23.70000076293945</v>
@@ -5128,7 +5128,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>24.41036796569824</v>
+        <v>24.41036415100098</v>
       </c>
       <c r="C180" t="n">
         <v>28.15999984741211</v>
@@ -5157,7 +5157,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>26.43784332275391</v>
+        <v>26.43784523010254</v>
       </c>
       <c r="C181" t="n">
         <v>30.30999946594238</v>
@@ -5215,7 +5215,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>30.27573013305664</v>
+        <v>30.27574348449707</v>
       </c>
       <c r="C183" t="n">
         <v>34.70999908447266</v>
@@ -5244,7 +5244,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>33.91489791870117</v>
+        <v>33.91490173339844</v>
       </c>
       <c r="C184" t="n">
         <v>38.68999862670898</v>
@@ -5273,7 +5273,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>35.52780914306641</v>
+        <v>35.52781295776367</v>
       </c>
       <c r="C185" t="n">
         <v>40.52999877929688</v>
@@ -5302,7 +5302,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>37.15824127197266</v>
+        <v>37.15825653076172</v>
       </c>
       <c r="C186" t="n">
         <v>42.38999938964844</v>
@@ -5331,7 +5331,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>36.29355621337891</v>
+        <v>36.29356002807617</v>
       </c>
       <c r="C187" t="n">
         <v>41.22999954223633</v>
@@ -5389,7 +5389,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>36.75129699707031</v>
+        <v>36.75128936767578</v>
       </c>
       <c r="C189" t="n">
         <v>41.75</v>
@@ -5418,7 +5418,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>37.55897903442383</v>
+        <v>37.5589714050293</v>
       </c>
       <c r="C190" t="n">
         <v>42.45000076293945</v>
@@ -5447,7 +5447,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>42.27485656738281</v>
+        <v>42.27486038208008</v>
       </c>
       <c r="C191" t="n">
         <v>47.77999877929688</v>
@@ -5476,7 +5476,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>39.34622955322266</v>
+        <v>39.34623336791992</v>
       </c>
       <c r="C192" t="n">
         <v>44.47000122070312</v>
@@ -5505,7 +5505,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>39.55340194702148</v>
+        <v>39.55339431762695</v>
       </c>
       <c r="C193" t="n">
         <v>44.4900016784668</v>
@@ -5534,7 +5534,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>41.02031707763672</v>
+        <v>41.02031326293945</v>
       </c>
       <c r="C194" t="n">
         <v>46.13999938964844</v>
@@ -5563,7 +5563,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>39.29557037353516</v>
+        <v>39.29557418823242</v>
       </c>
       <c r="C195" t="n">
         <v>44.20000076293945</v>
@@ -5592,7 +5592,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>36.82541275024414</v>
+        <v>36.82540893554688</v>
       </c>
       <c r="C196" t="n">
         <v>41.22000122070312</v>
@@ -5621,7 +5621,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>31.87605476379395</v>
+        <v>31.87604713439941</v>
       </c>
       <c r="C197" t="n">
         <v>35.68000030517578</v>
@@ -5650,7 +5650,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>33.23400115966797</v>
+        <v>33.23399353027344</v>
       </c>
       <c r="C198" t="n">
         <v>37.20000076293945</v>
@@ -5679,7 +5679,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>27.9713191986084</v>
+        <v>27.97132301330566</v>
       </c>
       <c r="C199" t="n">
         <v>31.1299991607666</v>
@@ -5708,7 +5708,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>30.3793888092041</v>
+        <v>30.37939262390137</v>
       </c>
       <c r="C200" t="n">
         <v>33.81000137329102</v>
@@ -5737,7 +5737,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>30.19968795776367</v>
+        <v>30.19968414306641</v>
       </c>
       <c r="C201" t="n">
         <v>33.61000061035156</v>
@@ -5766,7 +5766,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>27.31447601318359</v>
+        <v>27.31447792053223</v>
       </c>
       <c r="C202" t="n">
         <v>30.20000076293945</v>
@@ -5795,7 +5795,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>32.59648513793945</v>
+        <v>32.59648132324219</v>
       </c>
       <c r="C203" t="n">
         <v>36.04000091552734</v>
@@ -5882,7 +5882,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>32.27759170532227</v>
+        <v>32.2775993347168</v>
       </c>
       <c r="C206" t="n">
         <v>35.47999954223633</v>
@@ -5911,7 +5911,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>31.2041072845459</v>
+        <v>31.20410537719727</v>
       </c>
       <c r="C207" t="n">
         <v>34.29999923706055</v>
@@ -5940,7 +5940,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>26.18733215332031</v>
+        <v>26.18733596801758</v>
       </c>
       <c r="C208" t="n">
         <v>28.60000038146973</v>
@@ -5998,7 +5998,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>25.44566917419434</v>
+        <v>25.44566535949707</v>
       </c>
       <c r="C210" t="n">
         <v>27.79000091552734</v>
@@ -6027,7 +6027,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>26.47936820983887</v>
+        <v>26.47936630249023</v>
       </c>
       <c r="C211" t="n">
         <v>28.69000053405762</v>
@@ -6085,7 +6085,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>26.68141937255859</v>
+        <v>26.68141746520996</v>
       </c>
       <c r="C213" t="n">
         <v>28.67000007629395</v>
@@ -6114,7 +6114,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>25.48089027404785</v>
+        <v>25.48089408874512</v>
       </c>
       <c r="C214" t="n">
         <v>27.3799991607666</v>
@@ -6143,7 +6143,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>24.51303100585938</v>
+        <v>24.51302909851074</v>
       </c>
       <c r="C215" t="n">
         <v>26.34000015258789</v>
@@ -6172,7 +6172,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>28.60165023803711</v>
+        <v>28.60165214538574</v>
       </c>
       <c r="C216" t="n">
         <v>30.48999977111816</v>
@@ -6201,7 +6201,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>31.5846996307373</v>
+        <v>31.58470153808594</v>
       </c>
       <c r="C217" t="n">
         <v>33.66999816894531</v>
@@ -6230,7 +6230,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>31.90363693237305</v>
+        <v>31.90364837646484</v>
       </c>
       <c r="C218" t="n">
         <v>34.0099983215332</v>
@@ -6346,7 +6346,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>37.77754592895508</v>
+        <v>37.77753829956055</v>
       </c>
       <c r="C222" t="n">
         <v>39.9900016784668</v>
@@ -6375,7 +6375,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>37.79821395874023</v>
+        <v>37.7982177734375</v>
       </c>
       <c r="C223" t="n">
         <v>39.77000045776367</v>
@@ -6404,7 +6404,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>38.31143951416016</v>
+        <v>38.31144332885742</v>
       </c>
       <c r="C224" t="n">
         <v>40.31000137329102</v>
@@ -6462,7 +6462,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>37.95854568481445</v>
+        <v>37.95854949951172</v>
       </c>
       <c r="C226" t="n">
         <v>39.68000030517578</v>
@@ -6491,7 +6491,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>40.00571060180664</v>
+        <v>40.00570678710938</v>
       </c>
       <c r="C227" t="n">
         <v>41.81999969482422</v>
@@ -6520,7 +6520,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>45.4488525390625</v>
+        <v>45.44885635375977</v>
       </c>
       <c r="C228" t="n">
         <v>47.5099983215332</v>
@@ -6607,7 +6607,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>44.34534454345703</v>
+        <v>44.34534072875977</v>
       </c>
       <c r="C231" t="n">
         <v>46.09999847412109</v>
@@ -6636,7 +6636,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>40.39498901367188</v>
+        <v>40.39499664306641</v>
       </c>
       <c r="C232" t="n">
         <v>41.72999954223633</v>
@@ -6665,7 +6665,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>38.60418701171875</v>
+        <v>38.60418319702148</v>
       </c>
       <c r="C233" t="n">
         <v>39.88000106811523</v>
@@ -6723,7 +6723,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>46.07610321044922</v>
+        <v>46.07609939575195</v>
       </c>
       <c r="C235" t="n">
         <v>47.31999969482422</v>
@@ -6781,7 +6781,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>49.40619659423828</v>
+        <v>49.40620422363281</v>
       </c>
       <c r="C237" t="n">
         <v>50.7400016784668</v>
@@ -6810,7 +6810,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>50.51326370239258</v>
+        <v>50.51326751708984</v>
       </c>
       <c r="C238" t="n">
         <v>51.59000015258789</v>
@@ -6868,7 +6868,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>52.53026962280273</v>
+        <v>52.5302734375</v>
       </c>
       <c r="C240" t="n">
         <v>53.65000152587891</v>
@@ -6955,7 +6955,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>49.04354476928711</v>
+        <v>49.04354858398438</v>
       </c>
       <c r="C243" t="n">
         <v>49.83000183105469</v>
@@ -7013,7 +7013,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>52.91370010375977</v>
+        <v>52.9136962890625</v>
       </c>
       <c r="C245" t="n">
         <v>53.45999908447266</v>
@@ -7042,7 +7042,7 @@
         <v>46173</v>
       </c>
       <c r="B246" t="n">
-        <v>51.07270431518555</v>
+        <v>51.07270812988281</v>
       </c>
       <c r="C246" t="n">
         <v>51.59999847412109</v>
